--- a/Rules.xlsx
+++ b/Rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grouperenault-my.sharepoint.com/personal/anton_lysyy_renault_com/Documents/Recap/RENAULT/07_Achat_Projet/RGP_DIGITAL/010_IA/14 GIB ML/FANNY fichiers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="11_F25DC773A252ABDACC104851E99B5D4A5BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D02BDAD-5525-4206-9248-4A0C0C01CB9E}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_F25DC773A252ABDACC104851E99B5D4A5BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57728960-8544-4248-B10E-9FC7F5DB7346}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>CLIENT</t>
   </si>
@@ -180,6 +180,23 @@
   </si>
   <si>
     <t>Condition: "Part number != Part number replaced"</t>
+  </si>
+  <si>
+    <t>MESSAGE</t>
+  </si>
+  <si>
+    <t>"Salut! Je ne suis pas une intilligence artificielle, mais un programme écrit par Anton, pour t'aider à convertir un fichier standard harness type Yazaki. Faut que tu me depose le fichier maintenant!"</t>
+  </si>
+  <si>
+    <t>"Merci pour le fichier ! Je vais maintenant analyser le fichier avec les règles, que Arianne, Louise et Thomas ont spécifié dans leur dossier refinement, surtout :
+- la présence des colonnes obligatoires Client, Anc. Références, Nv. Références
+- la présence du compte fournisseur (COFOR) dans le fichier"</t>
+  </si>
+  <si>
+    <t>"Le fichier a l'air d'être bon, je vais extraire le tableau avec les colonnes Client, références, incoterm et les prix"</t>
+  </si>
+  <si>
+    <t>"je vais renommer les colonnes pour passer au titres standrards, mettre en forme le tableau"</t>
   </si>
 </sst>
 </file>
@@ -553,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -584,24 +601,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" thickBot="1">
+    <row r="2" spans="1:6" ht="69.599999999999994" thickBot="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
       <c r="F2" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1">
@@ -609,139 +620,121 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.2" thickBot="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="111" thickBot="1">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="B4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="79.8" thickBot="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" thickBot="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.2" thickBot="1">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>13</v>
+      <c r="B6" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="42" thickBot="1">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="1"/>
       <c r="F7" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="79.8" thickBot="1">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="42" thickBot="1">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="4" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" thickBot="1">
@@ -752,13 +745,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>19</v>
@@ -769,58 +762,138 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="27" thickBot="1">
+    <row r="12" spans="1:6" ht="15" thickBot="1">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="27" thickBot="1">
+    <row r="13" spans="1:6" ht="15" thickBot="1">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" thickBot="1">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" thickBot="1">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="27" thickBot="1">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="27" thickBot="1">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>19</v>
       </c>
     </row>
